--- a/data/2026/Grocery 2026/cleaned/sale_jan_26_cleaned.xlsx
+++ b/data/2026/Grocery 2026/cleaned/sale_jan_26_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,2210 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>001006P</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GELLETE PRESTO 5S R/SET</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>001017G</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GILLETTE MACH 3 TURBO 8PACK</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>667.37</v>
+      </c>
+      <c r="G3" t="n">
+        <v>700.74</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1401.48</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1334.74</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>001018H</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GILLETE VECTOR+ 4PACK</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="G4" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="H4" t="n">
+        <v>332</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2303.36</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2193.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="N4" t="n">
+        <v>188</v>
+      </c>
+      <c r="O4" t="n">
+        <v>156</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>001020S</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GILLETTE VICTOR+  R/SET</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>359.28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>342.16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>99</v>
+      </c>
+      <c r="O5" t="n">
+        <v>91</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>001022K</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GILLETTE 7 O CLOCK P-II R/BLADE 5</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75.56999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4444</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>44</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3325.08</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3166.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>66</v>
+      </c>
+      <c r="O6" t="n">
+        <v>22</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>001024A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GILLETTE 7 O CLOCK PLATINUM R/BLADE</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="H7" t="n">
+        <v>548</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>48</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1245.12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1185.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="N7" t="n">
+        <v>58</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>001026E</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GILLETTE WILMAN II PREMIUM</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>221</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1986.18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1891.68</v>
+      </c>
+      <c r="M8" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>001032T</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GILLETTE WILMAN I</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="L9" t="n">
+        <v>173.48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>001060L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>R/SET 7 O CLOCK EJECT S/P</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="G10" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="H10" t="n">
+        <v>344</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="L10" t="n">
+        <v>180.04</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>16</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>001061P</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GILLETTE  R/SET 7 O CLOCK P-II</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>77.01000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1078.14</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1026.76</v>
+      </c>
+      <c r="M11" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="N11" t="n">
+        <v>45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>001063Y</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GILLETTE MACH3 TURBO+ R/SET</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>172.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>181.22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>906.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>862.95</v>
+      </c>
+      <c r="M12" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>29</v>
+      </c>
+      <c r="O12" t="n">
+        <v>24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>001079K</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GILL SKIN GAURD SENSETIVE CART 2S</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>271.96</v>
+      </c>
+      <c r="G13" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4561</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="L13" t="n">
+        <v>271.96</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>001104L</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VI-JHON SHAVING CREAM</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>169.74</v>
+      </c>
+      <c r="L14" t="n">
+        <v>161.64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>155</v>
+      </c>
+      <c r="O14" t="n">
+        <v>146</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>001119A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>VI JOHN SHAVING CREAM MENTHOL 125</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" t="n">
+        <v>226.32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>001141S</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S/CREAM DETTOL</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="G16" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="H16" t="n">
+        <v>43</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2291.47</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2182.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="N16" t="n">
+        <v>155</v>
+      </c>
+      <c r="O16" t="n">
+        <v>112</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>001143U</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WILD STONE SHAVNGH CREAM 70 GM</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="n">
+        <v>564.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>537.3200000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="N17" t="n">
+        <v>131</v>
+      </c>
+      <c r="O17" t="n">
+        <v>117</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>001177X</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FOAM PARK AVENUE 200G</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="G18" t="n">
+        <v>119.41</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1074.69</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1023.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="N18" t="n">
+        <v>44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>35</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>001191A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BOMBAY SHAVING COMPANY SENSITIVE</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>138</v>
+      </c>
+      <c r="G19" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>238</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1159.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1104</v>
+      </c>
+      <c r="M19" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>001195V</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VI JOHN SAVING FOAM 400GM</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>146.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>154</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>770</v>
+      </c>
+      <c r="L20" t="n">
+        <v>733.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>54</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>001202N</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FA AFTER SHAVE LOTION 100 ML</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>105.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>105.42</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>001205A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WILD AFTER SHAVE 50 ML</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>68.20999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>477.47</v>
+      </c>
+      <c r="L22" t="n">
+        <v>454.72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>001283T</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TULIPS PERMIUM COTTON BALLS 50S BAG</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="G23" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="L23" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="N23" t="n">
+        <v>73</v>
+      </c>
+      <c r="O23" t="n">
+        <v>65</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>001284T</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TULIPS PREMIUM COTTROM BUDS 100JAR</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="H24" t="n">
+        <v>63</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>63</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2729.79</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2600.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="N24" t="n">
+        <v>63</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>001354L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AYURVEDA   HYDRAA  MOSIT SKIN</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>140.97</v>
+      </c>
+      <c r="G25" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3552.48</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3383.28</v>
+      </c>
+      <c r="M25" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>50</v>
+      </c>
+      <c r="O25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>001355K</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NIMSON/BODY/LOTION/500ML</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>159.38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>167.35</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>21</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3514.35</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3346.98</v>
+      </c>
+      <c r="M26" t="n">
+        <v>167.37</v>
+      </c>
+      <c r="N26" t="n">
+        <v>21</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>001363A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NIVEA SHEA SMOOTH BODY MILK 200 ML</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>167.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>176.13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5988.42</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5703.16</v>
+      </c>
+      <c r="M27" t="n">
+        <v>285.26</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>001426A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Everteen Natural Intimate Wash</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>207.92</v>
+      </c>
+      <c r="G28" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>207.92</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>60</v>
+      </c>
+      <c r="O28" t="n">
+        <v>59</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>002011A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AJAY SB 251 QUEST PRE SHAVING BRUSH</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="G29" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="H29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>213</v>
+      </c>
+      <c r="O29" t="n">
+        <v>203</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>002028L</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>S/BRUSH GELLETE (7 O CLOCK)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="G30" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13</v>
+      </c>
+      <c r="K30" t="n">
+        <v>500.37</v>
+      </c>
+      <c r="L30" t="n">
+        <v>476.58</v>
+      </c>
+      <c r="M30" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>002033K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ANCHOR JUNGLE KIDZ BRUSH</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="G31" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="H31" t="n">
+        <v>37</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>37</v>
+      </c>
+      <c r="K31" t="n">
+        <v>783.66</v>
+      </c>
+      <c r="L31" t="n">
+        <v>746.29</v>
+      </c>
+      <c r="M31" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>432</v>
+      </c>
+      <c r="O31" t="n">
+        <v>395</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>002045M</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ANCHOR HI TIP TOOTH BRUSH MEDIUM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="H32" t="n">
+        <v>159</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>159</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2227.59</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2121.06</v>
+      </c>
+      <c r="M32" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="N32" t="n">
+        <v>165</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>002052H</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>T/BRUSH COLGATE ZIG ZAG</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="L33" t="n">
+        <v>59</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>002063H</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>T/BRUSH OZETTE SPRING ACTION</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="H34" t="n">
+        <v>190</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>190</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3205.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3053.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>152</v>
+      </c>
+      <c r="N34" t="n">
+        <v>235</v>
+      </c>
+      <c r="O34" t="n">
+        <v>45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>002073P</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ORA-B CRISSCROSS 90.00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="G35" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="H35" t="n">
+        <v>98</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>98</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4063.08</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3870.02</v>
+      </c>
+      <c r="M35" t="n">
+        <v>193.06</v>
+      </c>
+      <c r="N35" t="n">
+        <v>240</v>
+      </c>
+      <c r="O35" t="n">
+        <v>142</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>002089K</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>COLGATE PLAX MOUTHWASH 250ML</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="G36" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>002090L</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LISTERINE MOUTHWASH 250 ML</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="G37" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>894.24</v>
+      </c>
+      <c r="L37" t="n">
+        <v>851.67</v>
+      </c>
+      <c r="M37" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>002102A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SPOTZERO TOILET BRUSH D/SIDE DRISTL</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="L38" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>002103A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SPOTZERO TOILET BRUSH WITH C/ROUND</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>140.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>294.64</v>
+      </c>
+      <c r="L39" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
